--- a/src/utils/sxsyzlzq/friends/qie/zz_qe_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/qie/zz_qe_level.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="11130" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="11550" windowHeight="10425" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="炼狱" sheetId="8" r:id="rId1"/>
-    <sheet name="港口" sheetId="6" r:id="rId2"/>
+    <sheet name="港口" sheetId="6" r:id="rId1"/>
+    <sheet name="炼狱" sheetId="8" r:id="rId2"/>
     <sheet name="帝国" sheetId="5" r:id="rId3"/>
     <sheet name="隐秘" sheetId="9" r:id="rId4"/>
   </sheets>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="72">
   <si>
     <t>名称</t>
   </si>
@@ -41,6 +41,69 @@
     <t>卡等</t>
   </si>
   <si>
+    <t>心灵黑洞</t>
+  </si>
+  <si>
+    <t>狡诈学徒</t>
+  </si>
+  <si>
+    <t>黑金勒索者</t>
+  </si>
+  <si>
+    <t>黑夜突袭</t>
+  </si>
+  <si>
+    <t>酗酒醉汉</t>
+  </si>
+  <si>
+    <t>不法交易</t>
+  </si>
+  <si>
+    <t>小计：</t>
+  </si>
+  <si>
+    <t>蓝色卡等：</t>
+  </si>
+  <si>
+    <t>海燕精卫</t>
+  </si>
+  <si>
+    <t>红海猎魔人</t>
+  </si>
+  <si>
+    <t>黑水伏击</t>
+  </si>
+  <si>
+    <t>黑金诈术师</t>
+  </si>
+  <si>
+    <t>星辰陨落</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>花剑绅士·翔</t>
+  </si>
+  <si>
+    <t>海燕·鲍莉</t>
+  </si>
+  <si>
+    <t>赤影·艾希尔</t>
+  </si>
+  <si>
+    <t>钢之咆哮·布瑞恩</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>港口卡等：</t>
+  </si>
+  <si>
     <t>冥河守卫</t>
   </si>
   <si>
@@ -50,12 +113,6 @@
     <t>烈焰风暴</t>
   </si>
   <si>
-    <t>小计：</t>
-  </si>
-  <si>
-    <t>蓝色卡等：</t>
-  </si>
-  <si>
     <t>碎颅魔</t>
   </si>
   <si>
@@ -80,9 +137,6 @@
     <t>恶灵魔焰</t>
   </si>
   <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
     <t>痛苦之心</t>
   </si>
   <si>
@@ -95,70 +149,10 @@
     <t>血翼·莉莉丝</t>
   </si>
   <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
     <t>炼狱卡等：</t>
   </si>
   <si>
-    <t>心灵黑洞</t>
-  </si>
-  <si>
-    <t>狡诈学徒</t>
-  </si>
-  <si>
-    <t>黑金勒索者</t>
-  </si>
-  <si>
-    <t>黑夜突袭</t>
-  </si>
-  <si>
-    <t>酗酒醉汉</t>
-  </si>
-  <si>
-    <t>不法交易</t>
-  </si>
-  <si>
-    <t>海燕精卫</t>
-  </si>
-  <si>
-    <t>红海猎魔人</t>
-  </si>
-  <si>
-    <t>黑水伏击</t>
-  </si>
-  <si>
-    <t>黑金诈术师</t>
-  </si>
-  <si>
-    <t>星辰陨落</t>
-  </si>
-  <si>
-    <t>花剑绅士·翔</t>
-  </si>
-  <si>
-    <t>海燕·鲍莉</t>
-  </si>
-  <si>
-    <t>赤影·艾希尔</t>
-  </si>
-  <si>
-    <t>钢之咆哮·布瑞恩</t>
-  </si>
-  <si>
-    <t>黑金三代目·梅森</t>
-  </si>
-  <si>
-    <t>港口卡等：</t>
-  </si>
-  <si>
     <t>圣殿弩手</t>
-  </si>
-  <si>
-    <t>增援战线</t>
   </si>
   <si>
     <t>田园守望者</t>
@@ -1215,6 +1209,289 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v>19.8571428571429</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2">
+        <f>AVERAGE(C14:C18)</f>
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="3">
+        <v>2</v>
+      </c>
+      <c r="C24" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="3">
+        <v>3</v>
+      </c>
+      <c r="C25" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="3">
+        <v>4</v>
+      </c>
+      <c r="C26" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="3">
+        <v>5</v>
+      </c>
+      <c r="C27" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="3">
+        <f>AVERAGE(C24:C27)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="4">
+        <f>AVERAGE(C2:C8,C14:C18,C24:C27)</f>
+        <v>20.3125</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
@@ -1236,7 +1513,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -1247,7 +1524,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -1258,7 +1535,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1">
         <v>4</v>
@@ -1279,10 +1556,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1">
         <f>AVERAGE(C2:C4)</f>
@@ -1292,7 +1569,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2">
         <v>2</v>
@@ -1303,7 +1580,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
@@ -1314,7 +1591,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2">
         <v>3</v>
@@ -1325,7 +1602,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
@@ -1336,7 +1613,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
@@ -1347,7 +1624,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B15" s="2">
         <v>5</v>
@@ -1358,24 +1635,24 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2">
         <v>5</v>
       </c>
       <c r="C16" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2">
         <v>6</v>
       </c>
       <c r="C17" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1390,19 +1667,19 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2">
         <f>AVERAGE(C10:C17)</f>
-        <v>20.375</v>
+        <v>20.625</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B23" s="3">
         <v>2</v>
@@ -1413,29 +1690,29 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B24" s="3">
         <v>3</v>
       </c>
       <c r="C24" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B25" s="3">
         <v>5</v>
       </c>
       <c r="C25" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B26" s="3">
         <v>6</v>
@@ -1456,14 +1733,14 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C23:C26)</f>
-        <v>16.75</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1471,305 +1748,11 @@
         <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C4,C10:C17,C23:C26)</f>
-        <v>19.7333333333333</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="1">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="1">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="1">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="1">
-        <f>AVERAGE(C2:C8)</f>
-        <v>19.5714285714286</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="2">
-        <v>2</v>
-      </c>
-      <c r="C15" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="2">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4</v>
-      </c>
-      <c r="C17" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="2">
-        <v>5</v>
-      </c>
-      <c r="C18" s="2">
         <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C14:C18)</f>
-        <v>20.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="3">
-        <v>2</v>
-      </c>
-      <c r="C24" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="3">
-        <v>3</v>
-      </c>
-      <c r="C25" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="3">
-        <v>4</v>
-      </c>
-      <c r="C26" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="3">
-        <v>5</v>
-      </c>
-      <c r="C27" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="3">
-        <v>7</v>
-      </c>
-      <c r="C28" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" s="3">
-        <f>AVERAGE(C24:C28)</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" s="4">
-        <f>AVERAGE(C2:C8,C14:C18,C24:C28)</f>
-        <v>19.4705882352941</v>
       </c>
     </row>
   </sheetData>
@@ -1802,7 +1785,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1">
         <v>3</v>
@@ -1813,88 +1796,88 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1">
         <v>3</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="1">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1">
-        <v>17</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1">
-        <f>AVERAGE(C2:C5)</f>
-        <v>20.5</v>
-      </c>
-      <c r="D8" s="2"/>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1">
+        <f>AVERAGE(C2:C4)</f>
+        <v>20.3333333333333</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2">
         <v>22</v>
@@ -1902,7 +1885,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14" s="2">
         <v>3</v>
@@ -1913,18 +1896,18 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
@@ -1935,7 +1918,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
@@ -1956,41 +1939,41 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2">
-        <f>AVERAGE(C11:C17)</f>
-        <v>20.4285714285714</v>
+        <f>AVERAGE(C10:C17)</f>
+        <v>20.375</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B23" s="3">
         <v>3</v>
       </c>
       <c r="C23" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B24" s="3">
         <v>4</v>
       </c>
       <c r="C24" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
@@ -2001,29 +1984,29 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B26" s="3">
         <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B27" s="3">
         <v>6</v>
       </c>
       <c r="C27" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B28" s="3">
         <v>7</v>
@@ -2034,7 +2017,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B29" s="3">
         <v>8</v>
@@ -2055,14 +2038,14 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C32" s="3">
         <f>AVERAGE(C23:C29)</f>
-        <v>17.1428571428571</v>
+        <v>17.7142857142857</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2070,18 +2053,18 @@
         <v>22</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C35" s="4">
-        <f>AVERAGE(C2:C5,C11:C17,C23:C29)</f>
-        <v>19.1666666666667</v>
+        <f>AVERAGE(C2:C4,C10:C17,C23:C29)</f>
+        <v>19.3333333333333</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C35 C8" formulaRange="1"/>
+    <ignoredError sqref="C7 C35" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2110,7 +2093,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -2121,7 +2104,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -2132,7 +2115,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -2143,7 +2126,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
@@ -2164,10 +2147,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1">
         <f>AVERAGE(C2:C5)</f>
@@ -2177,7 +2160,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
@@ -2188,7 +2171,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
@@ -2199,7 +2182,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
@@ -2210,7 +2193,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B14" s="2">
         <v>3</v>
@@ -2221,7 +2204,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B15" s="2">
         <v>5</v>
@@ -2232,7 +2215,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B16" s="2">
         <v>6</v>
@@ -2243,7 +2226,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B17" s="2">
         <v>7</v>
@@ -2264,7 +2247,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -2276,7 +2259,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B23" s="3">
         <v>3</v>
@@ -2287,7 +2270,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B24" s="3">
         <v>4</v>
@@ -2298,7 +2281,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B25" s="3">
         <v>5</v>
@@ -2309,7 +2292,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B26" s="3">
         <v>7</v>
@@ -2330,7 +2313,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
@@ -2345,7 +2328,7 @@
         <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C5,C11:C17,C23:C26)</f>
